--- a/artfynd/A 499-2026 artfynd.xlsx
+++ b/artfynd/A 499-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,41 +675,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67545429</v>
+        <v>67555310</v>
       </c>
       <c r="B2" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616954.5394608737</v>
+        <v>616955</v>
       </c>
       <c r="R2" t="n">
-        <v>6876800.046444229</v>
+        <v>6876800</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -750,19 +753,9 @@
           <t>2017-09-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-09-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,55 +783,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67545427</v>
+        <v>68604263</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gnarp, 3 km S, Hls</t>
+          <t>Jättendal-Gnarp, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616954.5394608737</v>
+        <v>616941</v>
       </c>
       <c r="R3" t="n">
-        <v>6876800.046444229</v>
+        <v>6876821</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,19 +851,14 @@
           <t>2017-09-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-09-13</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Skarp, bitter. Doft mjöl. Svartblå bas.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,56 +867,50 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jesper Hansson, Tony Svensson</t>
+          <t>Tony Svensson, Jesper Hansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67545432</v>
+        <v>67545427</v>
       </c>
       <c r="B4" t="n">
-        <v>88019</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616954.5394608737</v>
+        <v>616955</v>
       </c>
       <c r="R4" t="n">
-        <v>6876800.046444229</v>
+        <v>6876800</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -980,19 +955,9 @@
           <t>2017-09-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-09-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,15 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67555310</v>
+        <v>68604256</v>
       </c>
       <c r="B5" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,47 +996,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gnarp, 3 km S, Hls</t>
+          <t>Jättendal-Gnarp, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616954.5394608737</v>
+        <v>616979</v>
       </c>
       <c r="R5" t="n">
-        <v>6876800.046444229</v>
+        <v>6876829</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,77 +1053,61 @@
           <t>2017-09-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-09-13</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jesper Hansson, Tony Svensson</t>
+          <t>Tony Svensson, Jesper Hansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68604261</v>
+        <v>68604266</v>
       </c>
       <c r="B6" t="n">
-        <v>77532</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616906.5775345485</v>
+        <v>616945</v>
       </c>
       <c r="R6" t="n">
-        <v>6876812.027502269</v>
+        <v>6876796</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,19 +1150,9 @@
           <t>2017-09-13</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-09-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1179,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>68604263</v>
+        <v>67545429</v>
       </c>
       <c r="B7" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,37 +1190,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jättendal-Gnarp, Hls</t>
+          <t>Gnarp, 3 km S, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616940.6292674036</v>
+        <v>616955</v>
       </c>
       <c r="R7" t="n">
-        <v>6876821.191421655</v>
+        <v>6876800</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,81 +1249,62 @@
           <t>2017-09-13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2017-09-13</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Skarp, bitter. Doft mjöl. Svartblå bas.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tony Svensson, Jesper Hansson</t>
+          <t>Jesper Hansson, Tony Svensson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>68604266</v>
+        <v>68604255</v>
       </c>
       <c r="B8" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,10 +1314,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616944.7940021426</v>
+        <v>616987</v>
       </c>
       <c r="R8" t="n">
-        <v>6876795.950107658</v>
+        <v>6876822</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,19 +1347,9 @@
           <t>2017-09-13</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2017-09-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,6 +1373,300 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>67545432</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gnarp, 3 km S, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>616955</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6876800</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jesper Hansson, Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>68604257</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Jättendal-Gnarp, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>616978</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6876823</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tony Svensson, Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>68604261</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79351</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Jättendal-Gnarp, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>616907</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6876812</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2017-09-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tony Svensson, Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
